--- a/급여대장 양식1.xlsx
+++ b/급여대장 양식1.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0819893d08f6fe16/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{ECD2D223-140B-402D-84D9-955AABF94BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{803880FF-E380-4EB7-A049-7D8AED308F07}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="8_{ECD2D223-140B-402D-84D9-955AABF94BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF78ABE7-EBBE-41A7-983F-646633B303BD}"/>
   <bookViews>
-    <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" xr2:uid="{4509E15F-7645-4A6B-BB00-BF83DD045207}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4509E15F-7645-4A6B-BB00-BF83DD045207}"/>
   </bookViews>
   <sheets>
     <sheet name="1월급여" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1월급여'!$B$1:$N$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1월급여'!$B$1:$O$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,19 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="53">
-  <si>
-    <t>2023년 01월 직원급여 지급대장</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">상  호  명 : </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>대한민국 국세청</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="55">
   <si>
     <t>사원번호</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -182,10 +170,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>영업부</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>월정액</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -223,14 +207,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>아르바이트</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>판촉부</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>합        계</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -248,6 +224,38 @@
   </si>
   <si>
     <t>* 2026년 최저시급 10,320원</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>초정 육전밀면 갈비탕 전문점</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026년 03월 직원급여 지급대장</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>은행</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일용직</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>계약직</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대표이사</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>홀메니저</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>주방메니저</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -259,7 +267,7 @@
     <numFmt numFmtId="176" formatCode="#,##0_ ;[Red]\-#,##0\ "/>
     <numFmt numFmtId="177" formatCode="00\-000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -288,6 +296,15 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="22"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
@@ -493,9 +510,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -552,6 +566,24 @@
     <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -564,12 +596,6 @@
     <xf numFmtId="176" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -579,16 +605,7 @@
     <xf numFmtId="176" fontId="3" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -606,6 +623,59 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>201084</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>84666</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>550334</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>95165</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{021791C2-25E7-CF1A-F3D5-ADFB7507D0B6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8307917" y="84666"/>
+          <a:ext cx="1047750" cy="1005332"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -905,758 +975,820 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6192A564-4C34-460C-801F-FF6AE82DA01E}">
-  <dimension ref="B1:Y20"/>
-  <sheetFormatPr defaultRowHeight="18.2" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:Z21"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.796875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.75" style="1" customWidth="1"/>
     <col min="2" max="2" width="10.5" style="2" customWidth="1"/>
-    <col min="3" max="3" width="10.3984375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="15.8984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.8984375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.59765625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.09765625" style="1" customWidth="1"/>
-    <col min="9" max="10" width="9.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="16.3984375" style="1" customWidth="1"/>
-    <col min="15" max="15" width="12.19921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="24" width="11.296875" style="1" customWidth="1"/>
-    <col min="25" max="25" width="12.19921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="8.796875" style="1"/>
+    <col min="3" max="3" width="10.375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="15.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.125" style="1" customWidth="1"/>
+    <col min="10" max="11" width="9.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="16.375" style="1" customWidth="1"/>
+    <col min="16" max="16" width="12.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="25" width="11.25" style="1" customWidth="1"/>
+    <col min="26" max="26" width="12.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="8.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:25" ht="39.450000000000003" x14ac:dyDescent="0.4">
-      <c r="B1" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32"/>
-      <c r="V1" s="32"/>
-      <c r="W1" s="32"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="32"/>
-    </row>
-    <row r="2" spans="2:25" x14ac:dyDescent="0.4">
-      <c r="B2" s="2" t="s">
+    <row r="1" spans="1:26" ht="39" x14ac:dyDescent="0.3">
+      <c r="B1" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
+      <c r="V1" s="22"/>
+      <c r="W1" s="22"/>
+      <c r="X1" s="22"/>
+      <c r="Y1" s="22"/>
+      <c r="Z1" s="22"/>
+    </row>
+    <row r="2" spans="1:26" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
+      <c r="T2" s="35"/>
+      <c r="U2" s="35"/>
+      <c r="V2" s="35"/>
+      <c r="W2" s="35"/>
+      <c r="X2" s="35"/>
+      <c r="Y2" s="35"/>
+      <c r="Z2" s="35"/>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A3" s="35"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="35"/>
+      <c r="M3" s="35"/>
+      <c r="N3" s="35"/>
+      <c r="O3" s="35"/>
+      <c r="P3" s="35"/>
+      <c r="Q3" s="35"/>
+      <c r="R3" s="35"/>
+      <c r="S3" s="35"/>
+      <c r="T3" s="35"/>
+      <c r="U3" s="35"/>
+      <c r="V3" s="35"/>
+      <c r="W3" s="35"/>
+      <c r="X3" s="35"/>
+      <c r="Y3" s="35"/>
+      <c r="Z3" s="35"/>
+    </row>
+    <row r="4" spans="1:26" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D4" s="24" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="2:25" s="6" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="33" t="s">
+      <c r="E4" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="H4" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="28" t="s">
+      <c r="I4" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="F3" s="28" t="s">
+      <c r="J4" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="28" t="s">
+      <c r="K4" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="34" t="s">
+      <c r="L4" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="34" t="s">
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="24"/>
+      <c r="Q4" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="25" t="s">
+      <c r="R4" s="24"/>
+      <c r="S4" s="24"/>
+      <c r="T4" s="24"/>
+      <c r="U4" s="24"/>
+      <c r="V4" s="24"/>
+      <c r="W4" s="24"/>
+      <c r="X4" s="24"/>
+      <c r="Y4" s="24"/>
+      <c r="Z4" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="28" t="s">
+    </row>
+    <row r="5" spans="1:26" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="23"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="28"/>
-      <c r="M3" s="28"/>
-      <c r="N3" s="28"/>
-      <c r="O3" s="28"/>
-      <c r="P3" s="28" t="s">
+      <c r="M5" s="33"/>
+      <c r="N5" s="33"/>
+      <c r="O5" s="34"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="28"/>
-      <c r="R3" s="28"/>
-      <c r="S3" s="28"/>
-      <c r="T3" s="28"/>
-      <c r="U3" s="28"/>
-      <c r="V3" s="28"/>
-      <c r="W3" s="28"/>
-      <c r="X3" s="28"/>
-      <c r="Y3" s="28" t="s">
+      <c r="R5" s="33"/>
+      <c r="S5" s="33"/>
+      <c r="T5" s="34"/>
+      <c r="U5" s="32" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="2:25" s="6" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="33"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="29" t="s">
+      <c r="V5" s="34"/>
+      <c r="W5" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="L4" s="30"/>
-      <c r="M4" s="30"/>
-      <c r="N4" s="31"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="29" t="s">
+      <c r="X5" s="34"/>
+      <c r="Y5" s="4"/>
+      <c r="Z5" s="24"/>
+    </row>
+    <row r="6" spans="1:26" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="23"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="27"/>
+      <c r="L6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q4" s="30"/>
-      <c r="R4" s="30"/>
-      <c r="S4" s="31"/>
-      <c r="T4" s="29" t="s">
+      <c r="M6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="U4" s="31"/>
-      <c r="V4" s="29" t="s">
+      <c r="N6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="W4" s="31"/>
-      <c r="X4" s="5"/>
-      <c r="Y4" s="28"/>
-    </row>
-    <row r="5" spans="2:25" s="7" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="33"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="27"/>
-      <c r="K5" s="5" t="s">
+      <c r="O6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="P6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="M5" s="5" t="s">
+      <c r="Q6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="N5" s="5" t="s">
+      <c r="R6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="O5" s="5" t="s">
+      <c r="S6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="P5" s="5" t="s">
+      <c r="T6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="Q5" s="5" t="s">
+      <c r="U6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="R5" s="5" t="s">
+      <c r="V6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="S5" s="5" t="s">
+      <c r="W6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="T5" s="5" t="s">
+      <c r="X6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="U5" s="5" t="s">
+      <c r="Y6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z6" s="24"/>
+    </row>
+    <row r="7" spans="1:26" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="7">
+        <v>1</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="V5" s="5" t="s">
+      <c r="D7" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="W5" s="5" t="s">
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="X5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y5" s="28"/>
-    </row>
-    <row r="6" spans="2:25" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="8">
-        <v>21001</v>
-      </c>
-      <c r="C6" s="9" t="s">
+      <c r="H7" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="I7" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="J7" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9" t="s">
+      <c r="K7" s="8"/>
+      <c r="L7" s="9">
+        <v>2500000</v>
+      </c>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="10">
+        <f t="shared" ref="P7:P15" si="0">SUM(L7:O7)</f>
+        <v>2500000</v>
+      </c>
+      <c r="Q7" s="9">
+        <f>ROUNDDOWN(SUM(L7:O7)*3.545%,-1)</f>
+        <v>88620</v>
+      </c>
+      <c r="R7" s="9">
+        <f>ROUNDDOWN(Q7*12.81%,-1)</f>
+        <v>11350</v>
+      </c>
+      <c r="S7" s="9">
+        <f>ROUND(SUM(L7:O7)*4.5%,-1)</f>
+        <v>112500</v>
+      </c>
+      <c r="T7" s="9">
+        <f>ROUND(SUM(L7:O7)*0.9%,-1)</f>
+        <v>22500</v>
+      </c>
+      <c r="U7" s="9"/>
+      <c r="V7" s="9">
+        <f>ROUNDDOWN(U7*10%, -1)</f>
+        <v>0</v>
+      </c>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9"/>
+      <c r="Y7" s="10">
+        <f>SUM(Q7:X7)</f>
+        <v>234970</v>
+      </c>
+      <c r="Z7" s="11">
+        <f>P7-Y7</f>
+        <v>2265030</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="7">
+        <v>2</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="D8" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="H8" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J8" s="8">
+        <v>10320</v>
+      </c>
+      <c r="K8" s="8"/>
+      <c r="L8" s="9">
+        <v>2300000</v>
+      </c>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="10">
+        <f t="shared" si="0"/>
+        <v>2300000</v>
+      </c>
+      <c r="Q8" s="9">
+        <f>ROUNDDOWN(SUM(L8:O8)*3.545%,-1)</f>
+        <v>81530</v>
+      </c>
+      <c r="R8" s="9">
+        <f t="shared" ref="R8:R10" si="1">ROUNDDOWN(Q8*12.81%,-1)</f>
+        <v>10440</v>
+      </c>
+      <c r="S8" s="9">
+        <f>ROUND(SUM(L8:O8)*4.5%,-1)</f>
+        <v>103500</v>
+      </c>
+      <c r="T8" s="9">
+        <f>ROUND(SUM(L8:O8)*0.9%,-1)</f>
+        <v>20700</v>
+      </c>
+      <c r="U8" s="9"/>
+      <c r="V8" s="9">
+        <f t="shared" ref="V8:V10" si="2">ROUNDDOWN(U8*10%, -1)</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="9"/>
+      <c r="X8" s="9"/>
+      <c r="Y8" s="10">
+        <f t="shared" ref="Y8:Y15" si="3">SUM(Q8:X8)</f>
+        <v>216170</v>
+      </c>
+      <c r="Z8" s="11">
+        <f t="shared" ref="Z8:Z15" si="4">P8-Y8</f>
+        <v>2083830</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="7">
+        <v>3</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="J6" s="9"/>
-      <c r="K6" s="10">
-        <v>2500000</v>
-      </c>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="11">
-        <f>SUM(K6:N6)</f>
-        <v>2500000</v>
-      </c>
-      <c r="P6" s="10">
-        <f>ROUNDDOWN(SUM(K6:N6)*3.545%,-1)</f>
-        <v>88620</v>
-      </c>
-      <c r="Q6" s="10">
-        <f>ROUNDDOWN(P6*12.81%,-1)</f>
-        <v>11350</v>
-      </c>
-      <c r="R6" s="10">
-        <f>ROUND(SUM(K6:N6)*4.5%,-1)</f>
-        <v>112500</v>
-      </c>
-      <c r="S6" s="10">
-        <f>ROUND(SUM(K6:N6)*0.9%,-1)</f>
-        <v>22500</v>
-      </c>
-      <c r="T6" s="10"/>
-      <c r="U6" s="10">
-        <f>ROUNDDOWN(T6*10%, -1)</f>
-        <v>0</v>
-      </c>
-      <c r="V6" s="10"/>
-      <c r="W6" s="10"/>
-      <c r="X6" s="11">
-        <f>SUM(P6:W6)</f>
-        <v>234970</v>
-      </c>
-      <c r="Y6" s="12">
-        <f>O6-X6</f>
-        <v>2265030</v>
-      </c>
-    </row>
-    <row r="7" spans="2:25" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="8">
-        <v>22001</v>
-      </c>
-      <c r="C7" s="9" t="s">
+      <c r="D9" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9" t="s">
+      <c r="H9" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" s="8">
+        <v>10320</v>
+      </c>
+      <c r="K9" s="8"/>
+      <c r="L9" s="9">
+        <v>2100000</v>
+      </c>
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="10">
+        <f t="shared" si="0"/>
+        <v>2100000</v>
+      </c>
+      <c r="Q9" s="9">
+        <f>ROUNDDOWN(SUM(L9:O9)*3.545%,-1)</f>
+        <v>74440</v>
+      </c>
+      <c r="R9" s="9">
+        <f t="shared" si="1"/>
+        <v>9530</v>
+      </c>
+      <c r="S9" s="9">
+        <f>ROUND(SUM(L9:O9)*4.5%,-1)</f>
+        <v>94500</v>
+      </c>
+      <c r="T9" s="9">
+        <f>ROUND(SUM(L9:O9)*0.9%,-1)</f>
+        <v>18900</v>
+      </c>
+      <c r="U9" s="9"/>
+      <c r="V9" s="9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="W9" s="9"/>
+      <c r="X9" s="9"/>
+      <c r="Y9" s="10">
+        <f t="shared" si="3"/>
+        <v>197370</v>
+      </c>
+      <c r="Z9" s="11">
+        <f t="shared" si="4"/>
+        <v>1902630</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="7">
+        <v>4</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="J7" s="9"/>
-      <c r="K7" s="10">
-        <v>2300000</v>
-      </c>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="11">
-        <f>SUM(K7:N7)</f>
-        <v>2300000</v>
-      </c>
-      <c r="P7" s="10">
-        <f>ROUNDDOWN(SUM(K7:N7)*3.545%,-1)</f>
-        <v>81530</v>
-      </c>
-      <c r="Q7" s="10">
-        <f t="shared" ref="Q7:Q9" si="0">ROUNDDOWN(P7*12.81%,-1)</f>
-        <v>10440</v>
-      </c>
-      <c r="R7" s="10">
-        <f>ROUND(SUM(K7:N7)*4.5%,-1)</f>
-        <v>103500</v>
-      </c>
-      <c r="S7" s="10">
-        <f>ROUND(SUM(K7:N7)*0.9%,-1)</f>
-        <v>20700</v>
-      </c>
-      <c r="T7" s="10"/>
-      <c r="U7" s="10">
-        <f t="shared" ref="U7:U9" si="1">ROUNDDOWN(T7*10%, -1)</f>
-        <v>0</v>
-      </c>
-      <c r="V7" s="10"/>
-      <c r="W7" s="10"/>
-      <c r="X7" s="11">
-        <f t="shared" ref="X7:X14" si="2">SUM(P7:W7)</f>
-        <v>216170</v>
-      </c>
-      <c r="Y7" s="12">
-        <f t="shared" ref="Y7:Y14" si="3">O7-X7</f>
-        <v>2083830</v>
-      </c>
-    </row>
-    <row r="8" spans="2:25" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="8">
-        <v>22002</v>
-      </c>
-      <c r="C8" s="9" t="s">
+      <c r="D10" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9" t="s">
+      <c r="H10" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J10" s="8">
+        <v>10320</v>
+      </c>
+      <c r="K10" s="8"/>
+      <c r="L10" s="9">
+        <f>J10*8*22</f>
+        <v>1816320</v>
+      </c>
+      <c r="M10" s="9"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="10">
+        <f t="shared" si="0"/>
+        <v>1816320</v>
+      </c>
+      <c r="Q10" s="9">
+        <f>ROUNDDOWN(SUM(L10:O10)*3.545%,-1)</f>
+        <v>64380</v>
+      </c>
+      <c r="R10" s="9">
+        <f t="shared" si="1"/>
+        <v>8240</v>
+      </c>
+      <c r="S10" s="9">
+        <f>ROUND(SUM(L10:O10)*4.5%,-1)</f>
+        <v>81730</v>
+      </c>
+      <c r="T10" s="9">
+        <f>ROUND(SUM(L10:O10)*0.9%,-1)</f>
+        <v>16350</v>
+      </c>
+      <c r="U10" s="9"/>
+      <c r="V10" s="9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="9"/>
+      <c r="X10" s="9"/>
+      <c r="Y10" s="10">
+        <f t="shared" si="3"/>
+        <v>170700</v>
+      </c>
+      <c r="Z10" s="11">
+        <f t="shared" si="4"/>
+        <v>1645620</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="7"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="9"/>
+      <c r="P11" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="9"/>
+      <c r="R11" s="9"/>
+      <c r="S11" s="9"/>
+      <c r="T11" s="9"/>
+      <c r="U11" s="9"/>
+      <c r="V11" s="9"/>
+      <c r="W11" s="9"/>
+      <c r="X11" s="9"/>
+      <c r="Y11" s="10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Z11" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="B12" s="7"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="9"/>
+      <c r="P12" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="9"/>
+      <c r="R12" s="9"/>
+      <c r="S12" s="9"/>
+      <c r="T12" s="9"/>
+      <c r="U12" s="9"/>
+      <c r="V12" s="9"/>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Z12" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="B13" s="7"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
+      <c r="P13" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="9"/>
+      <c r="R13" s="9"/>
+      <c r="S13" s="9"/>
+      <c r="T13" s="9"/>
+      <c r="U13" s="9"/>
+      <c r="V13" s="9"/>
+      <c r="W13" s="9"/>
+      <c r="X13" s="9"/>
+      <c r="Y13" s="10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Z13" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="B14" s="7"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
+      <c r="P14" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="9"/>
+      <c r="R14" s="9"/>
+      <c r="S14" s="9"/>
+      <c r="T14" s="9"/>
+      <c r="U14" s="9"/>
+      <c r="V14" s="9"/>
+      <c r="W14" s="9"/>
+      <c r="X14" s="9"/>
+      <c r="Y14" s="10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Z14" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="13"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="16"/>
+      <c r="O15" s="16"/>
+      <c r="P15" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="16"/>
+      <c r="R15" s="16"/>
+      <c r="S15" s="16"/>
+      <c r="T15" s="16"/>
+      <c r="U15" s="16"/>
+      <c r="V15" s="16"/>
+      <c r="W15" s="16"/>
+      <c r="X15" s="16"/>
+      <c r="Y15" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Z15" s="18">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" s="5" customFormat="1" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="G8" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="J8" s="9"/>
-      <c r="K8" s="10">
-        <v>2100000</v>
-      </c>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
-      <c r="O8" s="11">
-        <f>SUM(K8:N8)</f>
-        <v>2100000</v>
-      </c>
-      <c r="P8" s="10">
-        <f>ROUNDDOWN(SUM(K8:N8)*3.545%,-1)</f>
-        <v>74440</v>
-      </c>
-      <c r="Q8" s="10">
-        <f t="shared" si="0"/>
-        <v>9530</v>
-      </c>
-      <c r="R8" s="10">
-        <f>ROUND(SUM(K8:N8)*4.5%,-1)</f>
-        <v>94500</v>
-      </c>
-      <c r="S8" s="10">
-        <f>ROUND(SUM(K8:N8)*0.9%,-1)</f>
-        <v>18900</v>
-      </c>
-      <c r="T8" s="10"/>
-      <c r="U8" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="V8" s="10"/>
-      <c r="W8" s="10"/>
-      <c r="X8" s="11">
-        <f t="shared" si="2"/>
-        <v>197370</v>
-      </c>
-      <c r="Y8" s="12">
-        <f t="shared" si="3"/>
-        <v>1902630</v>
-      </c>
-    </row>
-    <row r="9" spans="2:25" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="8">
-        <v>22003</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" s="9" t="s">
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="20">
+        <f>SUM(L7:L15)</f>
+        <v>8716320</v>
+      </c>
+      <c r="M16" s="20">
+        <f t="shared" ref="M16:Z16" si="5">SUM(M7:M15)</f>
+        <v>0</v>
+      </c>
+      <c r="N16" s="20">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O16" s="20">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P16" s="20">
+        <f t="shared" si="5"/>
+        <v>8716320</v>
+      </c>
+      <c r="Q16" s="20">
+        <f t="shared" si="5"/>
+        <v>308970</v>
+      </c>
+      <c r="R16" s="20">
+        <f t="shared" si="5"/>
+        <v>39560</v>
+      </c>
+      <c r="S16" s="20">
+        <f t="shared" si="5"/>
+        <v>392230</v>
+      </c>
+      <c r="T16" s="20">
+        <f t="shared" si="5"/>
+        <v>78450</v>
+      </c>
+      <c r="U16" s="20">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="20">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="20">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="20">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="20">
+        <f t="shared" si="5"/>
+        <v>819210</v>
+      </c>
+      <c r="Z16" s="20">
+        <f t="shared" si="5"/>
+        <v>7897110</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B19" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9" t="s">
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B20" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="9" t="s">
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B21" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="H9" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="I9" s="9">
-        <v>9620</v>
-      </c>
-      <c r="J9" s="9">
-        <v>8</v>
-      </c>
-      <c r="K9" s="10">
-        <f>I9*8*22</f>
-        <v>1693120</v>
-      </c>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10">
-        <f>I9*J9*1.5</f>
-        <v>115440</v>
-      </c>
-      <c r="N9" s="10" t="e">
-        <f>ROUNDUP(#REF!/40*I9*(40/5),-1)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="O9" s="11" t="e">
-        <f>SUM(K9:N9)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="P9" s="10" t="e">
-        <f>ROUNDDOWN(SUM(K9:N9)*3.545%,-1)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Q9" s="10" t="e">
-        <f t="shared" si="0"/>
-        <v>#REF!</v>
-      </c>
-      <c r="R9" s="10" t="e">
-        <f>ROUND(SUM(K9:N9)*4.5%,-1)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="S9" s="10" t="e">
-        <f>ROUND(SUM(K9:N9)*0.9%,-1)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="T9" s="10"/>
-      <c r="U9" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="V9" s="10"/>
-      <c r="W9" s="10"/>
-      <c r="X9" s="11" t="e">
-        <f t="shared" si="2"/>
-        <v>#REF!</v>
-      </c>
-      <c r="Y9" s="12" t="e">
-        <f t="shared" si="3"/>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="10" spans="2:25" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="8"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="11">
-        <f>SUM(K10:N10)</f>
-        <v>0</v>
-      </c>
-      <c r="P10" s="10"/>
-      <c r="Q10" s="10"/>
-      <c r="R10" s="10"/>
-      <c r="S10" s="10"/>
-      <c r="T10" s="10"/>
-      <c r="U10" s="10"/>
-      <c r="V10" s="10"/>
-      <c r="W10" s="10"/>
-      <c r="X10" s="11">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Y10" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="2:25" x14ac:dyDescent="0.4">
-      <c r="B11" s="8"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="11">
-        <f>SUM(K11:N11)</f>
-        <v>0</v>
-      </c>
-      <c r="P11" s="10"/>
-      <c r="Q11" s="10"/>
-      <c r="R11" s="10"/>
-      <c r="S11" s="10"/>
-      <c r="T11" s="10"/>
-      <c r="U11" s="10"/>
-      <c r="V11" s="10"/>
-      <c r="W11" s="10"/>
-      <c r="X11" s="11">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Y11" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="2:25" x14ac:dyDescent="0.4">
-      <c r="B12" s="8"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10"/>
-      <c r="O12" s="11">
-        <f>SUM(K12:N12)</f>
-        <v>0</v>
-      </c>
-      <c r="P12" s="10"/>
-      <c r="Q12" s="10"/>
-      <c r="R12" s="10"/>
-      <c r="S12" s="10"/>
-      <c r="T12" s="10"/>
-      <c r="U12" s="10"/>
-      <c r="V12" s="10"/>
-      <c r="W12" s="10"/>
-      <c r="X12" s="11">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Y12" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="2:25" x14ac:dyDescent="0.4">
-      <c r="B13" s="8"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="11">
-        <f>SUM(K13:N13)</f>
-        <v>0</v>
-      </c>
-      <c r="P13" s="10"/>
-      <c r="Q13" s="10"/>
-      <c r="R13" s="10"/>
-      <c r="S13" s="10"/>
-      <c r="T13" s="10"/>
-      <c r="U13" s="10"/>
-      <c r="V13" s="10"/>
-      <c r="W13" s="10"/>
-      <c r="X13" s="11">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Y13" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="2:25" ht="18.8" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B14" s="14"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="17"/>
-      <c r="N14" s="17"/>
-      <c r="O14" s="18">
-        <f>SUM(K14:N14)</f>
-        <v>0</v>
-      </c>
-      <c r="P14" s="17"/>
-      <c r="Q14" s="17"/>
-      <c r="R14" s="17"/>
-      <c r="S14" s="17"/>
-      <c r="T14" s="17"/>
-      <c r="U14" s="17"/>
-      <c r="V14" s="17"/>
-      <c r="W14" s="17"/>
-      <c r="X14" s="18">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Y14" s="19">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="2:25" s="6" customFormat="1" ht="18.8" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="20"/>
-      <c r="K15" s="21">
-        <f>SUM(K6:K14)</f>
-        <v>8593120</v>
-      </c>
-      <c r="L15" s="21">
-        <f t="shared" ref="L15:Y15" si="4">SUM(L6:L14)</f>
-        <v>0</v>
-      </c>
-      <c r="M15" s="21">
-        <f t="shared" si="4"/>
-        <v>115440</v>
-      </c>
-      <c r="N15" s="21" t="e">
-        <f t="shared" si="4"/>
-        <v>#REF!</v>
-      </c>
-      <c r="O15" s="21" t="e">
-        <f t="shared" si="4"/>
-        <v>#REF!</v>
-      </c>
-      <c r="P15" s="21" t="e">
-        <f t="shared" si="4"/>
-        <v>#REF!</v>
-      </c>
-      <c r="Q15" s="21" t="e">
-        <f t="shared" si="4"/>
-        <v>#REF!</v>
-      </c>
-      <c r="R15" s="21" t="e">
-        <f t="shared" si="4"/>
-        <v>#REF!</v>
-      </c>
-      <c r="S15" s="21" t="e">
-        <f t="shared" si="4"/>
-        <v>#REF!</v>
-      </c>
-      <c r="T15" s="21">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U15" s="21">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V15" s="21">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W15" s="21">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="X15" s="21" t="e">
-        <f t="shared" si="4"/>
-        <v>#REF!</v>
-      </c>
-      <c r="Y15" s="21" t="e">
-        <f t="shared" si="4"/>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B18" s="22" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B19" s="22" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B20" s="22" t="s">
-        <v>52</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="B1:Y1"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="G3:G5"/>
-    <mergeCell ref="H3:H5"/>
-    <mergeCell ref="I3:I5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="B15:H15"/>
-    <mergeCell ref="J3:J5"/>
-    <mergeCell ref="K3:O3"/>
-    <mergeCell ref="P3:X3"/>
-    <mergeCell ref="Y3:Y5"/>
-    <mergeCell ref="K4:N4"/>
-    <mergeCell ref="P4:S4"/>
-    <mergeCell ref="T4:U4"/>
-    <mergeCell ref="V4:W4"/>
+  <mergeCells count="20">
+    <mergeCell ref="B16:I16"/>
+    <mergeCell ref="K4:K6"/>
+    <mergeCell ref="L4:P4"/>
+    <mergeCell ref="Q4:Y4"/>
+    <mergeCell ref="Z4:Z6"/>
+    <mergeCell ref="L5:O5"/>
+    <mergeCell ref="Q5:T5"/>
+    <mergeCell ref="U5:V5"/>
+    <mergeCell ref="W5:X5"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="B1:Z1"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="G4:G6"/>
+    <mergeCell ref="H4:H6"/>
+    <mergeCell ref="I4:I6"/>
+    <mergeCell ref="J4:J6"/>
+    <mergeCell ref="F4:F6"/>
+    <mergeCell ref="A2:Z3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>